--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488143_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488143_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.786</v>
+        <v>4.9392</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0588</v>
+        <v>3.1135</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7272</v>
+        <v>1.8257</v>
       </c>
       <c r="G2" t="n">
         <v>4.2215</v>
@@ -610,13 +610,13 @@
         <v>0.9264</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0649</v>
+        <v>0.0883</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0124</v>
+        <v>0.0423</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0525</v>
+        <v>0.046</v>
       </c>
       <c r="V2" t="n">
         <v>0.6294</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1667</v>
+        <v>3.5891</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8236</v>
+        <v>4.1721</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6569</v>
+        <v>-0.583</v>
       </c>
       <c r="G3" t="n">
         <v>2.4158</v>
@@ -688,13 +688,13 @@
         <v>1.6676</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1025</v>
+        <v>0.3199</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1641</v>
+        <v>0.1844</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0617</v>
+        <v>0.1355</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6289</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7486</v>
+        <v>3.2459</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2609</v>
+        <v>1.4135</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4877</v>
+        <v>1.8324</v>
       </c>
       <c r="G4" t="n">
         <v>1.0089</v>
@@ -766,13 +766,13 @@
         <v>2.4087</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1132</v>
+        <v>-0.6159</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6901</v>
+        <v>-0.5375</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4231</v>
+        <v>-0.0784</v>
       </c>
       <c r="V4" t="n">
         <v>0.6294</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9303</v>
+        <v>2.1131</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8721</v>
+        <v>-0.6647999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8025</v>
+        <v>2.7778</v>
       </c>
       <c r="G5" t="n">
         <v>4.1228</v>
@@ -844,13 +844,13 @@
         <v>1.4823</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3454</v>
+        <v>0.5282</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.06710000000000001</v>
+        <v>0.1402</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4126</v>
+        <v>0.388</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3144</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7202</v>
+        <v>2.0741</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0344</v>
+        <v>0.4376</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6858</v>
+        <v>1.6365</v>
       </c>
       <c r="G6" t="n">
         <v>0.7047</v>
@@ -922,13 +922,13 @@
         <v>2.594</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4668</v>
+        <v>-0.1129</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4713</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0045</v>
+        <v>-0.0448</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4975</v>
+        <v>1.7787</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0372</v>
+        <v>1.2446</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4603</v>
+        <v>0.5341</v>
       </c>
       <c r="G7" t="n">
         <v>2.1696</v>
@@ -1000,13 +1000,13 @@
         <v>1.1117</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2455</v>
+        <v>0.0358</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1766</v>
+        <v>0.0308</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0689</v>
+        <v>0.005</v>
       </c>
       <c r="V7" t="n">
         <v>0.3144</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ -  GUERRA SALGUEIRO</t>
+          <t>D. CASTRO DIANEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.9775</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9441000000000001</v>
+        <v>1.0695</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-0.092</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9441000000000001</v>
+        <v>1.583</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3221</v>
+        <v>0.1253</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6221</v>
+        <v>1.4577</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9441000000000001</v>
+        <v>2.9021</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3221</v>
+        <v>0.1543</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6221</v>
+        <v>2.7478</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-1.3191</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.029</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-1.2901</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.6676</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.2092</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.0202</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.189</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
+          <t>J. RODRIGUEZ -  GUERRA SALGUEIRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8226</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4811</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3037</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4598</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9732</v>
+        <v>0.3221</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.433</v>
+        <v>0.6221</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0381</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4422</v>
+        <v>0.3221</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.404</v>
+        <v>0.6221</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.498</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.531</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.029</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6676</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.7832</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6491</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.1341</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3155</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3155</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. CASTRO DIANEZ</t>
+          <t>D. ESCAMILLA DE SANTOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4211</v>
+        <v>0.3007</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6115</v>
+        <v>1.4217</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1904</v>
+        <v>-1.121</v>
       </c>
       <c r="G10" t="n">
-        <v>1.583</v>
+        <v>1.6185</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1253</v>
+        <v>2.6799</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4577</v>
+        <v>-1.0614</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9021</v>
+        <v>1.2029</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1543</v>
+        <v>1.8036</v>
       </c>
       <c r="L10" t="n">
-        <v>2.7478</v>
+        <v>-0.6007</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3191</v>
+        <v>0.4156</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.029</v>
+        <v>0.8763</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2901</v>
+        <v>-0.4607</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1853</v>
+        <v>0.7411</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R10" t="n">
         <v>1.6676</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3472</v>
+        <v>-0.1707</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4377</v>
+        <v>-0.4281</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0905</v>
+        <v>0.2574</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6294</v>
+        <v>-1.8883</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.5733</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6294</v>
+        <v>-3.4616</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2357</v>
+        <v>0.0453</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0358</v>
+        <v>1.8947</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8001</v>
+        <v>-1.8493</v>
       </c>
       <c r="G11" t="n">
         <v>1.9351</v>
@@ -1312,13 +1312,13 @@
         <v>0.9264</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8177</v>
+        <v>0.6274</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1604</v>
+        <v>0.0193</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6573</v>
+        <v>0.6081</v>
       </c>
       <c r="V11" t="n">
         <v>-2.5172</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. ESCAMILLA DE SANTOS</t>
+          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2274</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3237</v>
+        <v>-2.0025</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0964</v>
+        <v>1.9344</v>
       </c>
       <c r="G12" t="n">
-        <v>1.6185</v>
+        <v>-0.4598</v>
       </c>
       <c r="H12" t="n">
-        <v>2.6799</v>
+        <v>0.9732</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.0614</v>
+        <v>-1.433</v>
       </c>
       <c r="J12" t="n">
-        <v>1.2029</v>
+        <v>0.0381</v>
       </c>
       <c r="K12" t="n">
-        <v>1.8036</v>
+        <v>0.4422</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6007</v>
+        <v>-0.404</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4156</v>
+        <v>-0.498</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8763</v>
+        <v>0.531</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4607</v>
+        <v>-1.029</v>
       </c>
       <c r="P12" t="n">
-        <v>0.7411</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R12" t="n">
         <v>1.6676</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.244</v>
+        <v>0.8925</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.526</v>
+        <v>0.1278</v>
       </c>
       <c r="U12" t="n">
-        <v>0.282</v>
+        <v>0.7648</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.8883</v>
+        <v>-0.3155</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5733</v>
+        <v>-0.3155</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.4616</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.5887</v>
+        <v>-0.6324</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.5019</v>
+        <v>-1.4472</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9132</v>
+        <v>0.8147</v>
       </c>
       <c r="G13" t="n">
         <v>0.9477</v>
@@ -1468,13 +1468,13 @@
         <v>2.0382</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0015</v>
+        <v>-0.0423</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1007</v>
+        <v>-0.046</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1022</v>
+        <v>0.0037</v>
       </c>
       <c r="V13" t="n">
         <v>0.315</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.2543</v>
+        <v>-2.5557</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.9031</v>
+        <v>-2.1307</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3512</v>
+        <v>-0.4251</v>
       </c>
       <c r="G14" t="n">
         <v>-2.6856</v>
@@ -1546,13 +1546,13 @@
         <v>2.2234</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2455</v>
+        <v>-0.056</v>
       </c>
       <c r="T14" t="n">
-        <v>0.388</v>
+        <v>0.1604</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1425</v>
+        <v>-0.2164</v>
       </c>
       <c r="V14" t="n">
         <v>0.0005</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>15.6572</v>
+        <v>16.7515</v>
       </c>
       <c r="E15" t="n">
-        <v>8.371800000000002</v>
+        <v>9.466100000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>7.285399999999998</v>
+        <v>7.285200000000001</v>
       </c>
       <c r="G15" t="n">
         <v>18.5263</v>
@@ -1624,16 +1624,16 @@
         <v>20.3815</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6091999999999999</v>
+        <v>1.7035</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.4485</v>
+        <v>-0.3542999999999999</v>
       </c>
       <c r="U15" t="n">
         <v>2.0579</v>
       </c>
       <c r="V15" t="n">
-        <v>-4.404999999999999</v>
+        <v>-4.405</v>
       </c>
       <c r="W15" t="n">
         <v>5.348799999999999</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.5952</v>
+        <v>4.7424</v>
       </c>
       <c r="E16" t="n">
-        <v>4.5876</v>
+        <v>4.2939</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0076</v>
+        <v>0.4486</v>
       </c>
       <c r="G16" t="n">
         <v>-0.6471</v>
@@ -1702,13 +1702,13 @@
         <v>3.7057</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3574</v>
+        <v>0.5046</v>
       </c>
       <c r="T16" t="n">
-        <v>0.199</v>
+        <v>-0.0948</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1584</v>
+        <v>0.5994</v>
       </c>
       <c r="V16" t="n">
         <v>6.9231</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.7034</v>
+        <v>3.5206</v>
       </c>
       <c r="E17" t="n">
-        <v>3.9308</v>
+        <v>4.4204</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2273</v>
+        <v>-0.8998</v>
       </c>
       <c r="G17" t="n">
         <v>1.8622</v>
@@ -1780,13 +1780,13 @@
         <v>2.4087</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9381</v>
+        <v>-0.1209</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8754</v>
+        <v>-0.3858</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.06270000000000001</v>
+        <v>0.2649</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6294</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. BARRIENTOS PRIETO</t>
+          <t>H. GREVELS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.38</v>
+        <v>0.0188</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9791</v>
+        <v>1.4616</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5991</v>
+        <v>-1.4428</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5717</v>
+        <v>-0.5453</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3168</v>
+        <v>-1.4084</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2548</v>
+        <v>0.8631</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.122</v>
+        <v>1.4557</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2878</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1659</v>
+        <v>2.0227</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4497</v>
+        <v>-2.001</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.029</v>
+        <v>-0.8414</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4207</v>
+        <v>-1.1596</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.6676</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4087</v>
+        <v>1.6676</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3213</v>
+        <v>0.4698</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3669</v>
+        <v>0.0059</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0455</v>
+        <v>0.4638</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3144</v>
+        <v>-1.5733</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3144</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>H. GREVELS</t>
+          <t>J. BARRIENTOS PRIETO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5127</v>
+        <v>0.0031</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3637</v>
+        <v>-0.7832</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8763</v>
+        <v>0.7864</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5453</v>
+        <v>-1.5717</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.4084</v>
+        <v>-0.3168</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8631</v>
+        <v>-1.2548</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4557</v>
+        <v>-0.122</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-0.2878</v>
       </c>
       <c r="L20" t="n">
-        <v>2.0227</v>
+        <v>0.1659</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.001</v>
+        <v>-1.4497</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8414</v>
+        <v>-0.029</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1596</v>
+        <v>-1.4207</v>
       </c>
       <c r="P20" t="n">
-        <v>1.6676</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6676</v>
+        <v>2.4087</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0617</v>
+        <v>0.7045</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.092</v>
+        <v>0.5627</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0303</v>
+        <v>0.1418</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.5733</v>
+        <v>0.3144</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.5733</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1874</v>
+        <v>-2.4898</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0991</v>
+        <v>-2.5888</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0883</v>
+        <v>0.0989</v>
       </c>
       <c r="G21" t="n">
         <v>-4.9064</v>
@@ -2092,13 +2092,13 @@
         <v>2.9646</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8312</v>
+        <v>0.5288</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7461</v>
+        <v>0.2565</v>
       </c>
       <c r="U21" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.2723</v>
       </c>
       <c r="V21" t="n">
         <v>1.8877</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3961</v>
+        <v>-3.5101</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6004</v>
+        <v>-2.8942</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7957</v>
+        <v>-0.6159</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2698</v>
@@ -2170,13 +2170,13 @@
         <v>1.4823</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1437</v>
+        <v>-0.2577</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4414</v>
+        <v>-0.7352</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2977</v>
+        <v>0.4775</v>
       </c>
       <c r="V22" t="n">
         <v>0.3144</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.5871</v>
+        <v>-4.1054</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2605</v>
+        <v>-2.0646</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3265</v>
+        <v>-2.0408</v>
       </c>
       <c r="G23" t="n">
         <v>-4.26</v>
@@ -2248,13 +2248,13 @@
         <v>2.0382</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6066</v>
+        <v>-0.125</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.669</v>
+        <v>-0.4731</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0624</v>
+        <v>0.3482</v>
       </c>
       <c r="V23" t="n">
         <v>-1.5733</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.1232</v>
+        <v>-7.0178</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.7726</v>
+        <v>-5.6746</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3506</v>
+        <v>-1.3431</v>
       </c>
       <c r="G24" t="n">
         <v>-3.2765</v>
@@ -2326,13 +2326,13 @@
         <v>1.4823</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1791</v>
+        <v>-0.0737</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.766</v>
+        <v>-0.6681</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5869</v>
+        <v>0.5944</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2589</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.2577</v>
+        <v>-7.3487</v>
       </c>
       <c r="E25" t="n">
         <v>-5.944</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.3137</v>
+        <v>-1.4047</v>
       </c>
       <c r="G25" t="n">
         <v>-5.4001</v>
@@ -2404,13 +2404,13 @@
         <v>1.297</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.19</v>
+        <v>-0.281</v>
       </c>
       <c r="T25" t="n">
         <v>-0.526</v>
       </c>
       <c r="U25" t="n">
-        <v>0.336</v>
+        <v>0.245</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-15.6573</v>
+        <v>-13.6986</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.2853</v>
+        <v>-7.285199999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-8.371700000000001</v>
+        <v>-6.4132</v>
       </c>
       <c r="G26" t="n">
         <v>-18.5264</v>
@@ -2452,7 +2452,7 @@
         <v>-16.5678</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.9586</v>
+        <v>-1.958600000000001</v>
       </c>
       <c r="J26" t="n">
         <v>5.400600000000001</v>
@@ -2482,13 +2482,13 @@
         <v>19.4551</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.6093</v>
+        <v>1.3494</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.0578</v>
+        <v>-2.0579</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4485</v>
+        <v>3.4073</v>
       </c>
       <c r="V26" t="n">
         <v>4.4047</v>
